--- a/317 Newell St/Results/Excels/Exec_Summary_Performance_KPIs.xlsx
+++ b/317 Newell St/Results/Excels/Exec_Summary_Performance_KPIs.xlsx
@@ -79,10 +79,10 @@
     <t>Rent/Purchase Price ratio</t>
   </si>
   <si>
-    <t>$13603.33</t>
-  </si>
-  <si>
-    <t>$-3571.99</t>
+    <t>$13003.33</t>
+  </si>
+  <si>
+    <t>$-3937.99</t>
   </si>
   <si>
     <t>$37328.35</t>
@@ -91,235 +91,235 @@
     <t>$43862.50</t>
   </si>
   <si>
-    <t>$22156.36</t>
-  </si>
-  <si>
-    <t>-8.20%</t>
+    <t>$21790.36</t>
+  </si>
+  <si>
+    <t>-8.93%</t>
   </si>
   <si>
     <t>-100.00%</t>
   </si>
   <si>
-    <t>3.60%</t>
-  </si>
-  <si>
-    <t>9.38%</t>
-  </si>
-  <si>
-    <t>$16732.10</t>
-  </si>
-  <si>
-    <t>$-1220.66</t>
+    <t>3.35%</t>
+  </si>
+  <si>
+    <t>8.97%</t>
+  </si>
+  <si>
+    <t>$15994.10</t>
+  </si>
+  <si>
+    <t>$-1700.36</t>
   </si>
   <si>
     <t>$41386.10</t>
   </si>
   <si>
-    <t>$24761.44</t>
-  </si>
-  <si>
-    <t>-2.48%</t>
-  </si>
-  <si>
-    <t>-43.55%</t>
-  </si>
-  <si>
-    <t>5.22%</t>
-  </si>
-  <si>
-    <t>11.54%</t>
-  </si>
-  <si>
-    <t>$17150.40</t>
-  </si>
-  <si>
-    <t>$-1177.63</t>
+    <t>$23915.74</t>
+  </si>
+  <si>
+    <t>-3.59%</t>
+  </si>
+  <si>
+    <t>-45.48%</t>
+  </si>
+  <si>
+    <t>4.89%</t>
+  </si>
+  <si>
+    <t>11.03%</t>
+  </si>
+  <si>
+    <t>$16393.95</t>
+  </si>
+  <si>
+    <t>$-1669.32</t>
   </si>
   <si>
     <t>$45587.08</t>
   </si>
   <si>
-    <t>$27548.16</t>
-  </si>
-  <si>
-    <t>-2.69%</t>
-  </si>
-  <si>
-    <t>-20.75%</t>
-  </si>
-  <si>
-    <t>5.25%</t>
-  </si>
-  <si>
-    <t>11.83%</t>
-  </si>
-  <si>
-    <t>$17579.16</t>
-  </si>
-  <si>
-    <t>$-1130.23</t>
+    <t>$26210.76</t>
+  </si>
+  <si>
+    <t>-3.81%</t>
+  </si>
+  <si>
+    <t>-22.70%</t>
+  </si>
+  <si>
+    <t>4.91%</t>
+  </si>
+  <si>
+    <t>11.31%</t>
+  </si>
+  <si>
+    <t>$16803.80</t>
+  </si>
+  <si>
+    <t>$-1634.21</t>
   </si>
   <si>
     <t>$49938.73</t>
   </si>
   <si>
-    <t>$30528.21</t>
-  </si>
-  <si>
-    <t>-2.59%</t>
-  </si>
-  <si>
-    <t>-11.38%</t>
-  </si>
-  <si>
-    <t>5.28%</t>
-  </si>
-  <si>
-    <t>12.12%</t>
-  </si>
-  <si>
-    <t>$18018.64</t>
-  </si>
-  <si>
-    <t>$-1078.37</t>
+    <t>$28686.83</t>
+  </si>
+  <si>
+    <t>-3.73%</t>
+  </si>
+  <si>
+    <t>-13.20%</t>
+  </si>
+  <si>
+    <t>4.94%</t>
+  </si>
+  <si>
+    <t>11.59%</t>
+  </si>
+  <si>
+    <t>$17223.90</t>
+  </si>
+  <si>
+    <t>$-1594.96</t>
   </si>
   <si>
     <t>$54448.98</t>
   </si>
   <si>
-    <t>$33713.88</t>
-  </si>
-  <si>
-    <t>-2.47%</t>
-  </si>
-  <si>
-    <t>-6.37%</t>
-  </si>
-  <si>
-    <t>5.32%</t>
-  </si>
-  <si>
-    <t>12.43%</t>
-  </si>
-  <si>
-    <t>$18469.11</t>
-  </si>
-  <si>
-    <t>$-1021.95</t>
+    <t>$31355.92</t>
+  </si>
+  <si>
+    <t>-3.64%</t>
+  </si>
+  <si>
+    <t>-8.05%</t>
+  </si>
+  <si>
+    <t>4.96%</t>
+  </si>
+  <si>
+    <t>11.88%</t>
+  </si>
+  <si>
+    <t>$17654.49</t>
+  </si>
+  <si>
+    <t>$-1551.45</t>
   </si>
   <si>
     <t>$59126.26</t>
   </si>
   <si>
-    <t>$37118.09</t>
-  </si>
-  <si>
-    <t>-2.34%</t>
-  </si>
-  <si>
-    <t>-3.28%</t>
-  </si>
-  <si>
-    <t>5.36%</t>
-  </si>
-  <si>
-    <t>12.74%</t>
-  </si>
-  <si>
-    <t>$18930.84</t>
-  </si>
-  <si>
-    <t>$-960.88</t>
+    <t>$34230.63</t>
+  </si>
+  <si>
+    <t>-3.55%</t>
+  </si>
+  <si>
+    <t>-4.84%</t>
+  </si>
+  <si>
+    <t>4.99%</t>
+  </si>
+  <si>
+    <t>12.18%</t>
+  </si>
+  <si>
+    <t>$18095.86</t>
+  </si>
+  <si>
+    <t>$-1503.61</t>
   </si>
   <si>
     <t>$63979.57</t>
   </si>
   <si>
-    <t>$40754.38</t>
-  </si>
-  <si>
-    <t>-2.20%</t>
-  </si>
-  <si>
-    <t>-1.22%</t>
-  </si>
-  <si>
-    <t>5.40%</t>
-  </si>
-  <si>
-    <t>13.06%</t>
-  </si>
-  <si>
-    <t>$19404.11</t>
-  </si>
-  <si>
-    <t>$-895.04</t>
+    <t>$37324.18</t>
+  </si>
+  <si>
+    <t>-3.44%</t>
+  </si>
+  <si>
+    <t>-2.65%</t>
+  </si>
+  <si>
+    <t>5.03%</t>
+  </si>
+  <si>
+    <t>12.48%</t>
+  </si>
+  <si>
+    <t>$18548.25</t>
+  </si>
+  <si>
+    <t>$-1451.34</t>
   </si>
   <si>
     <t>$69018.51</t>
   </si>
   <si>
-    <t>$44637.00</t>
-  </si>
-  <si>
-    <t>-2.05%</t>
-  </si>
-  <si>
-    <t>0.25%</t>
-  </si>
-  <si>
-    <t>5.45%</t>
-  </si>
-  <si>
-    <t>13.38%</t>
-  </si>
-  <si>
-    <t>$19889.21</t>
-  </si>
-  <si>
-    <t>$-824.33</t>
+    <t>$40650.50</t>
+  </si>
+  <si>
+    <t>-3.32%</t>
+  </si>
+  <si>
+    <t>-1.08%</t>
+  </si>
+  <si>
+    <t>5.06%</t>
+  </si>
+  <si>
+    <t>12.79%</t>
+  </si>
+  <si>
+    <t>$19011.96</t>
+  </si>
+  <si>
+    <t>$-1394.55</t>
   </si>
   <si>
     <t>$74253.30</t>
   </si>
   <si>
-    <t>$48780.97</t>
-  </si>
-  <si>
-    <t>-1.89%</t>
-  </si>
-  <si>
-    <t>1.34%</t>
-  </si>
-  <si>
-    <t>5.49%</t>
-  </si>
-  <si>
-    <t>13.72%</t>
-  </si>
-  <si>
-    <t>$20386.44</t>
-  </si>
-  <si>
-    <t>$-748.65</t>
+    <t>$44224.25</t>
+  </si>
+  <si>
+    <t>-3.19%</t>
+  </si>
+  <si>
+    <t>0.10%</t>
+  </si>
+  <si>
+    <t>5.10%</t>
+  </si>
+  <si>
+    <t>13.11%</t>
+  </si>
+  <si>
+    <t>$19487.26</t>
+  </si>
+  <si>
+    <t>$-1333.12</t>
   </si>
   <si>
     <t>$79694.87</t>
   </si>
   <si>
-    <t>$53202.05</t>
-  </si>
-  <si>
-    <t>-1.72%</t>
-  </si>
-  <si>
-    <t>2.17%</t>
-  </si>
-  <si>
-    <t>5.55%</t>
-  </si>
-  <si>
-    <t>14.06%</t>
+    <t>$48060.87</t>
+  </si>
+  <si>
+    <t>-3.05%</t>
+  </si>
+  <si>
+    <t>1.02%</t>
+  </si>
+  <si>
+    <t>5.14%</t>
+  </si>
+  <si>
+    <t>13.44%</t>
   </si>
 </sst>
 </file>
@@ -997,34 +997,34 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>10.66</v>
+        <v>11.15</v>
       </c>
       <c r="C10">
-        <v>8.67</v>
+        <v>9.07</v>
       </c>
       <c r="D10">
-        <v>8.449999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="E10">
-        <v>8.25</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F10">
-        <v>8.050000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="G10">
-        <v>7.85</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H10">
-        <v>7.66</v>
+        <v>8.01</v>
       </c>
       <c r="I10">
-        <v>7.47</v>
+        <v>7.82</v>
       </c>
       <c r="J10">
-        <v>7.29</v>
+        <v>7.63</v>
       </c>
       <c r="K10">
-        <v>7.11</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1032,34 +1032,34 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="C11">
+        <v>1.11</v>
+      </c>
+      <c r="D11">
+        <v>1.1</v>
+      </c>
+      <c r="E11">
+        <v>1.1</v>
+      </c>
+      <c r="F11">
+        <v>1.09</v>
+      </c>
+      <c r="G11">
+        <v>1.09</v>
+      </c>
+      <c r="H11">
+        <v>1.08</v>
+      </c>
+      <c r="I11">
+        <v>1.08</v>
+      </c>
+      <c r="J11">
         <v>1.07</v>
       </c>
-      <c r="D11">
+      <c r="K11">
         <v>1.07</v>
-      </c>
-      <c r="E11">
-        <v>1.06</v>
-      </c>
-      <c r="F11">
-        <v>1.06</v>
-      </c>
-      <c r="G11">
-        <v>1.06</v>
-      </c>
-      <c r="H11">
-        <v>1.05</v>
-      </c>
-      <c r="I11">
-        <v>1.05</v>
-      </c>
-      <c r="J11">
-        <v>1.04</v>
-      </c>
-      <c r="K11">
-        <v>1.04</v>
       </c>
     </row>
     <row r="12" spans="1:11">
